--- a/artfynd/A 56985-2024 artfynd.xlsx
+++ b/artfynd/A 56985-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121702161</v>
+        <v>121702069</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555294</v>
+        <v>555311</v>
       </c>
       <c r="R2" t="n">
-        <v>6401327</v>
+        <v>6401348</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121702069</v>
+        <v>121701590</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -848,14 +848,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön2, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555311</v>
+        <v>555341</v>
       </c>
       <c r="R3" t="n">
-        <v>6401348</v>
+        <v>6401293</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121701590</v>
+        <v>121701717</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,17 +973,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>gransjön2, Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555341</v>
+        <v>555333</v>
       </c>
       <c r="R4" t="n">
-        <v>6401293</v>
+        <v>6401327</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121702324</v>
+        <v>121702161</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555309</v>
+        <v>555294</v>
       </c>
       <c r="R5" t="n">
-        <v>6401150</v>
+        <v>6401327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121702548</v>
+        <v>121702324</v>
       </c>
       <c r="B6" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,30 +1187,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1223,14 +1223,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>gransjön , Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555179</v>
+        <v>555309</v>
       </c>
       <c r="R6" t="n">
-        <v>6401285</v>
+        <v>6401150</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121701717</v>
+        <v>121702352</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1352,13 +1352,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555333</v>
+        <v>555318</v>
       </c>
       <c r="R7" t="n">
-        <v>6401327</v>
+        <v>6401174</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121702352</v>
+        <v>121702548</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,30 +1437,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1473,14 +1473,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön , Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555318</v>
+        <v>555179</v>
       </c>
       <c r="R8" t="n">
-        <v>6401174</v>
+        <v>6401285</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,10 +1550,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121740548</v>
+        <v>121733911</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1562,39 +1562,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555286</v>
+        <v>555334</v>
       </c>
       <c r="R9" t="n">
-        <v>6401213</v>
+        <v>6401210</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1635,17 +1635,28 @@
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1664,10 +1675,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121733911</v>
+        <v>121740548</v>
       </c>
       <c r="B10" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1676,39 +1687,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1716,10 +1727,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555334</v>
+        <v>555286</v>
       </c>
       <c r="R10" t="n">
-        <v>6401210</v>
+        <v>6401213</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1749,28 +1760,17 @@
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56985-2024 artfynd.xlsx
+++ b/artfynd/A 56985-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121702069</v>
+        <v>121701590</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -723,14 +723,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön2, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555311</v>
+        <v>555341</v>
       </c>
       <c r="R2" t="n">
-        <v>6401348</v>
+        <v>6401293</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121701590</v>
+        <v>121702161</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -848,14 +848,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>gransjön2, Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555341</v>
+        <v>555294</v>
       </c>
       <c r="R3" t="n">
-        <v>6401293</v>
+        <v>6401327</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121701717</v>
+        <v>121702548</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,30 +937,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,17 +973,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön , Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555333</v>
+        <v>555179</v>
       </c>
       <c r="R4" t="n">
-        <v>6401327</v>
+        <v>6401285</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121702161</v>
+        <v>121702324</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555294</v>
+        <v>555309</v>
       </c>
       <c r="R5" t="n">
-        <v>6401327</v>
+        <v>6401150</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121702324</v>
+        <v>121702352</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555309</v>
+        <v>555318</v>
       </c>
       <c r="R6" t="n">
-        <v>6401150</v>
+        <v>6401174</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121702352</v>
+        <v>121701717</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1352,13 +1352,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555318</v>
+        <v>555333</v>
       </c>
       <c r="R7" t="n">
-        <v>6401174</v>
+        <v>6401327</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121702548</v>
+        <v>121702069</v>
       </c>
       <c r="B8" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,30 +1437,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1473,14 +1473,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>gransjön , Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555179</v>
+        <v>555311</v>
       </c>
       <c r="R8" t="n">
-        <v>6401285</v>
+        <v>6401348</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,7 +1550,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121733911</v>
+        <v>121733758</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1598,14 +1598,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön , Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555334</v>
+        <v>555324</v>
       </c>
       <c r="R9" t="n">
-        <v>6401210</v>
+        <v>6401365</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1675,10 +1675,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121740548</v>
+        <v>121733911</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1687,39 +1687,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555286</v>
+        <v>555334</v>
       </c>
       <c r="R10" t="n">
-        <v>6401213</v>
+        <v>6401210</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1760,17 +1760,28 @@
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1789,10 +1800,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121733758</v>
+        <v>121740548</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1801,50 +1812,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>gransjön , Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555324</v>
+        <v>555286</v>
       </c>
       <c r="R11" t="n">
-        <v>6401365</v>
+        <v>6401213</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1874,28 +1885,17 @@
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56985-2024 artfynd.xlsx
+++ b/artfynd/A 56985-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121701590</v>
+        <v>121702232</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -723,14 +723,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>gransjön2, Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555341</v>
+        <v>555294</v>
       </c>
       <c r="R2" t="n">
-        <v>6401293</v>
+        <v>6401327</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121702161</v>
+        <v>121702548</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,30 +812,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -848,14 +848,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön , Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555294</v>
+        <v>555179</v>
       </c>
       <c r="R3" t="n">
-        <v>6401327</v>
+        <v>6401285</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121702548</v>
+        <v>121702069</v>
       </c>
       <c r="B4" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,30 +937,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,14 +973,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>gransjön , Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555179</v>
+        <v>555311</v>
       </c>
       <c r="R4" t="n">
-        <v>6401285</v>
+        <v>6401348</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121702352</v>
+        <v>121701717</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555318</v>
+        <v>555333</v>
       </c>
       <c r="R6" t="n">
-        <v>6401174</v>
+        <v>6401327</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121701717</v>
+        <v>121702352</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1352,13 +1352,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555333</v>
+        <v>555318</v>
       </c>
       <c r="R7" t="n">
-        <v>6401327</v>
+        <v>6401174</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,7 +1425,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121702069</v>
+        <v>121701590</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1473,14 +1473,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön2, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555311</v>
+        <v>555341</v>
       </c>
       <c r="R8" t="n">
-        <v>6401348</v>
+        <v>6401293</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,10 +1550,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121733758</v>
+        <v>121740548</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1562,50 +1562,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>gransjön , Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555324</v>
+        <v>555286</v>
       </c>
       <c r="R9" t="n">
-        <v>6401365</v>
+        <v>6401213</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1635,28 +1635,17 @@
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1800,10 +1789,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121740548</v>
+        <v>121733758</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1812,50 +1801,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön , Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555286</v>
+        <v>555324</v>
       </c>
       <c r="R11" t="n">
-        <v>6401213</v>
+        <v>6401365</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1885,17 +1874,28 @@
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56985-2024 artfynd.xlsx
+++ b/artfynd/A 56985-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121702232</v>
+        <v>121702352</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555294</v>
+        <v>555318</v>
       </c>
       <c r="R2" t="n">
-        <v>6401327</v>
+        <v>6401174</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121702548</v>
+        <v>121701590</v>
       </c>
       <c r="B3" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,30 +812,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -848,14 +848,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>gransjön , Sm</t>
+          <t>gransjön2, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555179</v>
+        <v>555341</v>
       </c>
       <c r="R3" t="n">
-        <v>6401285</v>
+        <v>6401293</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121701717</v>
+        <v>121702232</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555333</v>
+        <v>555294</v>
       </c>
       <c r="R6" t="n">
         <v>6401327</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121702352</v>
+        <v>121701717</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1352,13 +1352,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555318</v>
+        <v>555333</v>
       </c>
       <c r="R7" t="n">
-        <v>6401174</v>
+        <v>6401327</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121701590</v>
+        <v>121702548</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,30 +1437,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1473,14 +1473,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>gransjön2, Sm</t>
+          <t>gransjön , Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555341</v>
+        <v>555179</v>
       </c>
       <c r="R8" t="n">
-        <v>6401293</v>
+        <v>6401285</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1664,7 +1664,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121733911</v>
+        <v>121733758</v>
       </c>
       <c r="B10" t="n">
         <v>98113</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1712,14 +1712,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön , Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555334</v>
+        <v>555324</v>
       </c>
       <c r="R10" t="n">
-        <v>6401210</v>
+        <v>6401365</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1789,7 +1789,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121733758</v>
+        <v>121733911</v>
       </c>
       <c r="B11" t="n">
         <v>98113</v>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1837,14 +1837,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>gransjön , Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555324</v>
+        <v>555334</v>
       </c>
       <c r="R11" t="n">
-        <v>6401365</v>
+        <v>6401210</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 56985-2024 artfynd.xlsx
+++ b/artfynd/A 56985-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121701590</v>
+        <v>121702232</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -848,14 +848,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>gransjön2, Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555341</v>
+        <v>555294</v>
       </c>
       <c r="R3" t="n">
-        <v>6401293</v>
+        <v>6401327</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121702232</v>
+        <v>121702548</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,30 +1187,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1223,14 +1223,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön , Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555294</v>
+        <v>555179</v>
       </c>
       <c r="R6" t="n">
-        <v>6401327</v>
+        <v>6401285</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121701717</v>
+        <v>121701590</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1348,17 +1348,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön2, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555333</v>
+        <v>555341</v>
       </c>
       <c r="R7" t="n">
-        <v>6401327</v>
+        <v>6401293</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121702548</v>
+        <v>121701717</v>
       </c>
       <c r="B8" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,30 +1437,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1473,17 +1473,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>gransjön , Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555179</v>
+        <v>555333</v>
       </c>
       <c r="R8" t="n">
-        <v>6401285</v>
+        <v>6401327</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,10 +1550,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121740548</v>
+        <v>121733911</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1562,39 +1562,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555286</v>
+        <v>555334</v>
       </c>
       <c r="R9" t="n">
-        <v>6401213</v>
+        <v>6401210</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1635,17 +1635,28 @@
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1789,10 +1800,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121733911</v>
+        <v>121740548</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1801,39 +1812,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1841,10 +1852,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555334</v>
+        <v>555286</v>
       </c>
       <c r="R11" t="n">
-        <v>6401210</v>
+        <v>6401213</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1874,28 +1885,17 @@
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56985-2024 artfynd.xlsx
+++ b/artfynd/A 56985-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121702352</v>
+        <v>121702232</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555318</v>
+        <v>555294</v>
       </c>
       <c r="R2" t="n">
-        <v>6401174</v>
+        <v>6401327</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121702232</v>
+        <v>121702548</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,30 +812,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -848,14 +848,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön , Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555294</v>
+        <v>555179</v>
       </c>
       <c r="R3" t="n">
-        <v>6401327</v>
+        <v>6401285</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121702069</v>
+        <v>121702324</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555311</v>
+        <v>555309</v>
       </c>
       <c r="R4" t="n">
-        <v>6401348</v>
+        <v>6401150</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121702324</v>
+        <v>121701590</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1098,14 +1098,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön2, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555309</v>
+        <v>555341</v>
       </c>
       <c r="R5" t="n">
-        <v>6401150</v>
+        <v>6401293</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121702548</v>
+        <v>121702352</v>
       </c>
       <c r="B6" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,30 +1187,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1223,14 +1223,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>gransjön , Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555179</v>
+        <v>555318</v>
       </c>
       <c r="R6" t="n">
-        <v>6401285</v>
+        <v>6401174</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121701590</v>
+        <v>121701717</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1348,17 +1348,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>gransjön2, Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555341</v>
+        <v>555333</v>
       </c>
       <c r="R7" t="n">
-        <v>6401293</v>
+        <v>6401327</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,7 +1425,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121701717</v>
+        <v>121702069</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1477,13 +1477,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555333</v>
+        <v>555311</v>
       </c>
       <c r="R8" t="n">
-        <v>6401327</v>
+        <v>6401348</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1675,10 +1675,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121733758</v>
+        <v>121740548</v>
       </c>
       <c r="B10" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1687,50 +1687,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>gransjön , Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555324</v>
+        <v>555286</v>
       </c>
       <c r="R10" t="n">
-        <v>6401365</v>
+        <v>6401213</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1760,28 +1760,17 @@
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1800,10 +1789,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121740548</v>
+        <v>121733758</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1812,50 +1801,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön , Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555286</v>
+        <v>555324</v>
       </c>
       <c r="R11" t="n">
-        <v>6401213</v>
+        <v>6401365</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1885,17 +1874,28 @@
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56985-2024 artfynd.xlsx
+++ b/artfynd/A 56985-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121702232</v>
+        <v>121702324</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555294</v>
+        <v>555309</v>
       </c>
       <c r="R2" t="n">
-        <v>6401327</v>
+        <v>6401150</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121702548</v>
+        <v>121702069</v>
       </c>
       <c r="B3" t="n">
-        <v>105218</v>
+        <v>98131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,30 +812,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -848,14 +848,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>gransjön , Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555179</v>
+        <v>555311</v>
       </c>
       <c r="R3" t="n">
-        <v>6401285</v>
+        <v>6401348</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121702324</v>
+        <v>121701717</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555309</v>
+        <v>555333</v>
       </c>
       <c r="R4" t="n">
-        <v>6401150</v>
+        <v>6401327</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121701590</v>
+        <v>121702232</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1098,14 +1098,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>gransjön2, Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555341</v>
+        <v>555294</v>
       </c>
       <c r="R5" t="n">
-        <v>6401293</v>
+        <v>6401327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,7 +1178,7 @@
         <v>121702352</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121701717</v>
+        <v>121701590</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1348,17 +1348,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön2, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555333</v>
+        <v>555341</v>
       </c>
       <c r="R7" t="n">
-        <v>6401327</v>
+        <v>6401293</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121702069</v>
+        <v>121702548</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>105236</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,30 +1437,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1473,14 +1473,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön , Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555311</v>
+        <v>555179</v>
       </c>
       <c r="R8" t="n">
-        <v>6401348</v>
+        <v>6401285</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,10 +1550,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121733911</v>
+        <v>121733758</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1598,14 +1598,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön , Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555334</v>
+        <v>555324</v>
       </c>
       <c r="R9" t="n">
-        <v>6401210</v>
+        <v>6401365</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1678,7 +1678,7 @@
         <v>121740548</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121733758</v>
+        <v>121733911</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1837,14 +1837,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>gransjön , Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555324</v>
+        <v>555334</v>
       </c>
       <c r="R11" t="n">
-        <v>6401365</v>
+        <v>6401210</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 56985-2024 artfynd.xlsx
+++ b/artfynd/A 56985-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121702324</v>
+        <v>121702161</v>
       </c>
       <c r="B2" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555309</v>
+        <v>555294</v>
       </c>
       <c r="R2" t="n">
-        <v>6401150</v>
+        <v>6401327</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121702069</v>
+        <v>121702324</v>
       </c>
       <c r="B3" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555311</v>
+        <v>555309</v>
       </c>
       <c r="R3" t="n">
-        <v>6401348</v>
+        <v>6401150</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121701717</v>
+        <v>121701590</v>
       </c>
       <c r="B4" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,17 +973,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön2, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555333</v>
+        <v>555341</v>
       </c>
       <c r="R4" t="n">
-        <v>6401327</v>
+        <v>6401293</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121702232</v>
+        <v>121702069</v>
       </c>
       <c r="B5" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555294</v>
+        <v>555311</v>
       </c>
       <c r="R5" t="n">
-        <v>6401327</v>
+        <v>6401348</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121702352</v>
+        <v>121701717</v>
       </c>
       <c r="B6" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555318</v>
+        <v>555333</v>
       </c>
       <c r="R6" t="n">
-        <v>6401174</v>
+        <v>6401327</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121701590</v>
+        <v>121702352</v>
       </c>
       <c r="B7" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1348,14 +1348,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>gransjön2, Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555341</v>
+        <v>555318</v>
       </c>
       <c r="R7" t="n">
-        <v>6401293</v>
+        <v>6401174</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1428,7 +1428,7 @@
         <v>121702548</v>
       </c>
       <c r="B8" t="n">
-        <v>105236</v>
+        <v>105238</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1550,10 +1550,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121733758</v>
+        <v>121740548</v>
       </c>
       <c r="B9" t="n">
-        <v>98131</v>
+        <v>57381</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1562,50 +1562,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>gransjön , Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555324</v>
+        <v>555286</v>
       </c>
       <c r="R9" t="n">
-        <v>6401365</v>
+        <v>6401213</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1635,28 +1635,17 @@
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1675,10 +1664,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121740548</v>
+        <v>121733758</v>
       </c>
       <c r="B10" t="n">
-        <v>57381</v>
+        <v>98133</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1687,50 +1676,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön , Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555286</v>
+        <v>555324</v>
       </c>
       <c r="R10" t="n">
-        <v>6401213</v>
+        <v>6401365</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1760,17 +1749,28 @@
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>121733911</v>
       </c>
       <c r="B11" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 56985-2024 artfynd.xlsx
+++ b/artfynd/A 56985-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121702161</v>
+        <v>121701717</v>
       </c>
       <c r="B2" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555294</v>
+        <v>555333</v>
       </c>
       <c r="R2" t="n">
         <v>6401327</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121702324</v>
+        <v>121701590</v>
       </c>
       <c r="B3" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -848,14 +848,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön2, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555309</v>
+        <v>555341</v>
       </c>
       <c r="R3" t="n">
-        <v>6401150</v>
+        <v>6401293</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121701590</v>
+        <v>121702548</v>
       </c>
       <c r="B4" t="n">
-        <v>98133</v>
+        <v>105245</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,30 +937,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,14 +973,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>gransjön2, Sm</t>
+          <t>gransjön , Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555341</v>
+        <v>555179</v>
       </c>
       <c r="R4" t="n">
-        <v>6401293</v>
+        <v>6401285</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,7 +1053,7 @@
         <v>121702069</v>
       </c>
       <c r="B5" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121701717</v>
+        <v>121702232</v>
       </c>
       <c r="B6" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555333</v>
+        <v>555294</v>
       </c>
       <c r="R6" t="n">
         <v>6401327</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1303,7 +1303,7 @@
         <v>121702352</v>
       </c>
       <c r="B7" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121702548</v>
+        <v>121702324</v>
       </c>
       <c r="B8" t="n">
-        <v>105238</v>
+        <v>98140</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,30 +1437,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1473,14 +1473,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>gransjön , Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555179</v>
+        <v>555309</v>
       </c>
       <c r="R8" t="n">
-        <v>6401285</v>
+        <v>6401150</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1667,7 +1667,7 @@
         <v>121733758</v>
       </c>
       <c r="B10" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>121733911</v>
       </c>
       <c r="B11" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 56985-2024 artfynd.xlsx
+++ b/artfynd/A 56985-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121701717</v>
+        <v>121702324</v>
       </c>
       <c r="B2" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555333</v>
+        <v>555309</v>
       </c>
       <c r="R2" t="n">
-        <v>6401327</v>
+        <v>6401150</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121701590</v>
+        <v>121702548</v>
       </c>
       <c r="B3" t="n">
-        <v>98140</v>
+        <v>105254</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,30 +812,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -848,14 +848,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>gransjön2, Sm</t>
+          <t>gransjön , Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555341</v>
+        <v>555179</v>
       </c>
       <c r="R3" t="n">
-        <v>6401293</v>
+        <v>6401285</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121702548</v>
+        <v>121701590</v>
       </c>
       <c r="B4" t="n">
-        <v>105245</v>
+        <v>98149</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,30 +937,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,14 +973,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>gransjön , Sm</t>
+          <t>gransjön2, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555179</v>
+        <v>555341</v>
       </c>
       <c r="R4" t="n">
-        <v>6401285</v>
+        <v>6401293</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121702069</v>
+        <v>121702161</v>
       </c>
       <c r="B5" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555311</v>
+        <v>555294</v>
       </c>
       <c r="R5" t="n">
-        <v>6401348</v>
+        <v>6401327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121702232</v>
+        <v>121702069</v>
       </c>
       <c r="B6" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555294</v>
+        <v>555311</v>
       </c>
       <c r="R6" t="n">
-        <v>6401327</v>
+        <v>6401348</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1303,7 +1303,7 @@
         <v>121702352</v>
       </c>
       <c r="B7" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121702324</v>
+        <v>121701717</v>
       </c>
       <c r="B8" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1477,13 +1477,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555309</v>
+        <v>555333</v>
       </c>
       <c r="R8" t="n">
-        <v>6401150</v>
+        <v>6401327</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1553,7 +1553,7 @@
         <v>121740548</v>
       </c>
       <c r="B9" t="n">
-        <v>57381</v>
+        <v>57385</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121733758</v>
+        <v>121733911</v>
       </c>
       <c r="B10" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1712,14 +1712,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>gransjön , Sm</t>
+          <t>gransjön, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555324</v>
+        <v>555334</v>
       </c>
       <c r="R10" t="n">
-        <v>6401365</v>
+        <v>6401210</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1789,10 +1789,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121733911</v>
+        <v>121733758</v>
       </c>
       <c r="B11" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1837,14 +1837,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>gransjön, Sm</t>
+          <t>gransjön , Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555334</v>
+        <v>555324</v>
       </c>
       <c r="R11" t="n">
-        <v>6401210</v>
+        <v>6401365</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
